--- a/Assets/GameData/Excel/item.xlsx
+++ b/Assets/GameData/Excel/item.xlsx
@@ -26,8 +26,72 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Apple</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Apple:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+1装备
+2消耗品
+3货币
+9假道具
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Apple:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+1灰色 垃圾
+2白色
+3绿色
+4蓝色
+5橙色
+6紫色
+7...</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>item_id</t>
   </si>
@@ -47,6 +111,9 @@
     <t>category</t>
   </si>
   <si>
+    <t>show_in_bag</t>
+  </si>
+  <si>
     <t>max_stack_size</t>
   </si>
   <si>
@@ -56,6 +123,9 @@
     <t>rarity</t>
   </si>
   <si>
+    <t>can_trade</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -74,6 +144,9 @@
     <t>类别</t>
   </si>
   <si>
+    <t>进背包</t>
+  </si>
+  <si>
     <t>最大堆叠</t>
   </si>
   <si>
@@ -83,10 +156,31 @@
     <t>稀有度</t>
   </si>
   <si>
+    <t>可交易</t>
+  </si>
+  <si>
     <t>新手木剑</t>
   </si>
   <si>
+    <t>为每个新手准备的初始武器</t>
+  </si>
+  <si>
     <t>新手布衣</t>
+  </si>
+  <si>
+    <t>为每个新手准备的初始装备</t>
+  </si>
+  <si>
+    <t>经验值</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>新手hp恢复药水</t>
+  </si>
+  <si>
+    <t>缓慢恢复生命值，在30秒内回复共60生命值</t>
   </si>
 </sst>
 </file>
@@ -99,7 +193,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +344,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1231,20 +1336,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="8.38461538461539" customWidth="1"/>
-    <col min="2" max="3" width="10.3076923076923" customWidth="1"/>
+    <col min="2" max="2" width="17.4615384615385" customWidth="1"/>
+    <col min="3" max="3" width="30.0961538461538" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="7.46153846153846" customWidth="1"/>
-    <col min="6" max="6" width="9.07692307692308" customWidth="1"/>
-    <col min="7" max="7" width="15.9230769230769" customWidth="1"/>
-    <col min="8" max="8" width="7.53846153846154" customWidth="1"/>
-    <col min="9" max="9" width="8.15384615384615" customWidth="1"/>
+    <col min="6" max="7" width="9.07692307692308" customWidth="1"/>
+    <col min="8" max="8" width="15.9230769230769" customWidth="1"/>
+    <col min="9" max="9" width="7.53846153846154" customWidth="1"/>
+    <col min="10" max="10" width="8.15384615384615" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1272,42 +1378,57 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>100001</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1319,15 +1440,24 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>100002</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1339,11 +1469,99 @@
         <v>1</v>
       </c>
       <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>900001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>300001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
         <v>1</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>200001</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Assets/GameData/Excel/item.xlsx
+++ b/Assets/GameData/Excel/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24600" windowHeight="13440"/>
+    <workbookView windowWidth="28660" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>item_id</t>
   </si>
@@ -165,22 +165,34 @@
     <t>为每个新手准备的初始武器</t>
   </si>
   <si>
+    <t>sword</t>
+  </si>
+  <si>
     <t>新手布衣</t>
   </si>
   <si>
     <t>为每个新手准备的初始装备</t>
   </si>
   <si>
+    <t>armor</t>
+  </si>
+  <si>
     <t>经验值</t>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
+    <t>coins</t>
+  </si>
+  <si>
     <t>新手hp恢复药水</t>
   </si>
   <si>
     <t>缓慢恢复生命值，在30秒内回复共60生命值</t>
+  </si>
+  <si>
+    <t>hp</t>
   </si>
 </sst>
 </file>
@@ -1430,6 +1442,9 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -1454,10 +1469,13 @@
         <v>100002</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1483,7 +1501,7 @@
         <v>900001</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -1509,7 +1527,10 @@
         <v>300001</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1535,10 +1556,13 @@
         <v>200001</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
       </c>
       <c r="F7">
         <v>2</v>
